--- a/AR_Catalogue.xlsx
+++ b/AR_Catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domor\fyp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07848C94-2036-4873-9A2D-5CCDD95DCFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E92570-AD57-41D4-B0A4-B801037BA322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{6D07EECD-DCBB-46BD-9A5A-D37A0019639E}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9691" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9686" uniqueCount="148">
   <si>
     <t>AR_ID</t>
   </si>
@@ -444,13 +444,55 @@
     <t>Beta-Delta</t>
   </si>
   <si>
-    <t>Beta -&gt; Dropped -&gt; Alpha -&gt; Dropped</t>
-  </si>
-  <si>
     <t>file not found!</t>
   </si>
   <si>
-    <t>08 Beta</t>
+    <t>Beta -&gt; Beta-Gamma -&gt; Beta -&gt; Beta-Gamma -&gt; Beta</t>
+  </si>
+  <si>
+    <t>Alpha -&gt; H-alpha Plages</t>
+  </si>
+  <si>
+    <t>Beta-Gamma -&gt; Beta-Gamma-Delta -&gt; Beta-Gamma -&gt; Beta</t>
+  </si>
+  <si>
+    <t>Beta-Gamma -&gt; Beta-Gamma-Delta</t>
+  </si>
+  <si>
+    <t>Beta -&gt; Alpha -&gt; H-alpha Plages</t>
+  </si>
+  <si>
+    <t>Beta-Gamma -&gt; Beta-Delta -&gt; Beta -&gt; Beta-Gamma -&gt; Beta -&gt; Alpha</t>
+  </si>
+  <si>
+    <t>Beta-Gamma -&gt; Beta -&gt; Alpha -&gt; H-alpha Plages</t>
+  </si>
+  <si>
+    <t>Alpha -&gt; H-alpha Plages -&gt; Beta -&gt; Alpha -&gt; H-alpha Plages</t>
+  </si>
+  <si>
+    <t>Beta-Gamma -&gt;  Beta-Gamma-Delta -&gt; Beta-Delta -&gt; Beta-Gamma-Delta</t>
+  </si>
+  <si>
+    <t>Alpha -&gt; Beta -&gt; H-alpha Plages</t>
+  </si>
+  <si>
+    <t>Beta -&gt; H-alpha Plages -&gt; Alpha -&gt; H-alpha Plages</t>
+  </si>
+  <si>
+    <t>Beta -&gt; H-alpha Plages</t>
+  </si>
+  <si>
+    <t>Beta-Gamma -&gt; Beta-Gamma-Delta -&gt; Beta -&gt; H-alpha Plages</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Beta -&gt; Alpha</t>
+  </si>
+  <si>
+    <t>Beta -&gt; Alpha -&gt; H-alpha Plages -&gt; Beta</t>
+  </si>
+  <si>
+    <t>Beta -&gt; Beta-Gamma -&gt; Beta -&gt; Alpha -&gt; Beta -&gt; Alpha -&gt; H-alpha Plages</t>
   </si>
 </sst>
 </file>
@@ -1442,7 +1484,7 @@
   <cols>
     <col min="2" max="2" width="9.9296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.86328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.73046875" customWidth="1"/>
+    <col min="4" max="4" width="76.9296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2351,8 +2393,8 @@
       <c r="C53" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D53" t="s">
-        <v>42</v>
+      <c r="D53" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="E53" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2369,8 +2411,8 @@
       <c r="C54" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D54" t="s">
-        <v>42</v>
+      <c r="D54" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="E54" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2387,8 +2429,8 @@
       <c r="C55" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D55" t="s">
-        <v>42</v>
+      <c r="D55" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="E55" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2405,8 +2447,8 @@
       <c r="C56" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D56" t="s">
-        <v>42</v>
+      <c r="D56" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="E56" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2694,7 +2736,7 @@
         <v>61</v>
       </c>
       <c r="D72" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="E72" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2712,7 +2754,7 @@
         <v>61</v>
       </c>
       <c r="D73" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="E73" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2730,7 +2772,7 @@
         <v>85</v>
       </c>
       <c r="D74" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="E74" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2748,7 +2790,7 @@
         <v>61</v>
       </c>
       <c r="D75" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="E75" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2766,7 +2808,7 @@
         <v>61</v>
       </c>
       <c r="D76" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="E76" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2784,7 +2826,7 @@
         <v>61</v>
       </c>
       <c r="D77" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="E77" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2802,7 +2844,7 @@
         <v>61</v>
       </c>
       <c r="D78" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="E78" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2820,7 +2862,7 @@
         <v>85</v>
       </c>
       <c r="D79" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="E79" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2838,7 +2880,7 @@
         <v>61</v>
       </c>
       <c r="D80" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="E80" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2856,7 +2898,7 @@
         <v>61</v>
       </c>
       <c r="D81" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="E81" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2874,7 +2916,7 @@
         <v>61</v>
       </c>
       <c r="D82" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="E82" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2892,7 +2934,7 @@
         <v>61</v>
       </c>
       <c r="D83" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="E83" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2910,7 +2952,7 @@
         <v>61</v>
       </c>
       <c r="D84" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="E84" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -2928,7 +2970,7 @@
         <v>61</v>
       </c>
       <c r="D85" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="E85" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3054,7 +3096,7 @@
         <v>18</v>
       </c>
       <c r="D92" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="E92" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3072,7 +3114,7 @@
         <v>129</v>
       </c>
       <c r="D93" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="E93" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3090,7 +3132,7 @@
         <v>129</v>
       </c>
       <c r="D94" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="E94" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3108,7 +3150,7 @@
         <v>129</v>
       </c>
       <c r="D95" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="E95" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3126,7 +3168,7 @@
         <v>129</v>
       </c>
       <c r="D96" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="E96" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3143,8 +3185,8 @@
       <c r="C97" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D97" t="s">
-        <v>69</v>
+      <c r="D97" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="E97" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3161,8 +3203,8 @@
       <c r="C98" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D98" t="s">
-        <v>69</v>
+      <c r="D98" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="E98" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3179,8 +3221,8 @@
       <c r="C99" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D99" t="s">
-        <v>69</v>
+      <c r="D99" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="E99" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3197,8 +3239,8 @@
       <c r="C100" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D100" t="s">
-        <v>69</v>
+      <c r="D100" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="E100" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3215,8 +3257,8 @@
       <c r="C101" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D101" t="s">
-        <v>69</v>
+      <c r="D101" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="E101" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3324,7 +3366,7 @@
         <v>85</v>
       </c>
       <c r="D107" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E107" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3342,7 +3384,7 @@
         <v>85</v>
       </c>
       <c r="D108" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E108" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3360,7 +3402,7 @@
         <v>126</v>
       </c>
       <c r="D109" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E109" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3378,7 +3420,7 @@
         <v>126</v>
       </c>
       <c r="D110" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E110" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3396,7 +3438,7 @@
         <v>126</v>
       </c>
       <c r="D111" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E111" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3414,7 +3456,7 @@
         <v>126</v>
       </c>
       <c r="D112" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E112" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3432,7 +3474,7 @@
         <v>126</v>
       </c>
       <c r="D113" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E113" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3450,7 +3492,7 @@
         <v>126</v>
       </c>
       <c r="D114" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E114" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3468,7 +3510,7 @@
         <v>126</v>
       </c>
       <c r="D115" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E115" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3486,7 +3528,7 @@
         <v>126</v>
       </c>
       <c r="D116" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E116" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3504,7 +3546,7 @@
         <v>85</v>
       </c>
       <c r="D117" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E117" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3522,7 +3564,7 @@
         <v>85</v>
       </c>
       <c r="D118" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E118" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3540,7 +3582,7 @@
         <v>61</v>
       </c>
       <c r="D119" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E119" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3558,7 +3600,7 @@
         <v>128</v>
       </c>
       <c r="D120" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E120" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3576,7 +3618,7 @@
         <v>85</v>
       </c>
       <c r="D121" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="E121" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3594,7 +3636,7 @@
         <v>126</v>
       </c>
       <c r="D122" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="E122" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3612,7 +3654,7 @@
         <v>126</v>
       </c>
       <c r="D123" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="E123" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3630,7 +3672,7 @@
         <v>126</v>
       </c>
       <c r="D124" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="E124" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3648,7 +3690,7 @@
         <v>126</v>
       </c>
       <c r="D125" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="E125" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3666,7 +3708,7 @@
         <v>126</v>
       </c>
       <c r="D126" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="E126" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3684,7 +3726,7 @@
         <v>126</v>
       </c>
       <c r="D127" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="E127" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3702,7 +3744,7 @@
         <v>126</v>
       </c>
       <c r="D128" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="E128" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3720,7 +3762,7 @@
         <v>126</v>
       </c>
       <c r="D129" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="E129" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3738,7 +3780,7 @@
         <v>126</v>
       </c>
       <c r="D130" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="E130" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3756,7 +3798,7 @@
         <v>126</v>
       </c>
       <c r="D131" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="E131" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3774,7 +3816,7 @@
         <v>126</v>
       </c>
       <c r="D132" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="E132" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3792,7 +3834,7 @@
         <v>126</v>
       </c>
       <c r="D133" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="E133" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3810,7 +3852,7 @@
         <v>128</v>
       </c>
       <c r="D134" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="E134" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3828,7 +3870,7 @@
         <v>61</v>
       </c>
       <c r="D135" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E135" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3846,7 +3888,7 @@
         <v>61</v>
       </c>
       <c r="D136" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E136" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3864,7 +3906,7 @@
         <v>61</v>
       </c>
       <c r="D137" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E137" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3882,7 +3924,7 @@
         <v>18</v>
       </c>
       <c r="D138" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E138" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3900,7 +3942,7 @@
         <v>129</v>
       </c>
       <c r="D139" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E139" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3918,7 +3960,7 @@
         <v>129</v>
       </c>
       <c r="D140" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E140" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3936,7 +3978,7 @@
         <v>61</v>
       </c>
       <c r="D141" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="E141" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3954,7 +3996,7 @@
         <v>61</v>
       </c>
       <c r="D142" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="E142" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3972,7 +4014,7 @@
         <v>85</v>
       </c>
       <c r="D143" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="E143" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -3990,7 +4032,7 @@
         <v>61</v>
       </c>
       <c r="D144" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="E144" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4008,7 +4050,7 @@
         <v>61</v>
       </c>
       <c r="D145" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="E145" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4026,7 +4068,7 @@
         <v>61</v>
       </c>
       <c r="D146" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="E146" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4170,7 +4212,7 @@
         <v>85</v>
       </c>
       <c r="D154" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="E154" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4188,7 +4230,7 @@
         <v>130</v>
       </c>
       <c r="D155" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="E155" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4206,7 +4248,7 @@
         <v>61</v>
       </c>
       <c r="D156" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="E156" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4224,7 +4266,7 @@
         <v>85</v>
       </c>
       <c r="D157" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="E157" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4242,7 +4284,7 @@
         <v>85</v>
       </c>
       <c r="D158" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="E158" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4260,7 +4302,7 @@
         <v>85</v>
       </c>
       <c r="D159" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="E159" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4278,7 +4320,7 @@
         <v>85</v>
       </c>
       <c r="D160" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="E160" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4296,7 +4338,7 @@
         <v>61</v>
       </c>
       <c r="D161" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="E161" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4314,7 +4356,7 @@
         <v>61</v>
       </c>
       <c r="D162" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="E162" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4332,7 +4374,7 @@
         <v>18</v>
       </c>
       <c r="D163" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="E163" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4350,7 +4392,7 @@
         <v>18</v>
       </c>
       <c r="D164" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="E164" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4368,7 +4410,7 @@
         <v>18</v>
       </c>
       <c r="D165" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="E165" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4386,7 +4428,7 @@
         <v>18</v>
       </c>
       <c r="D166" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="E166" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4404,7 +4446,7 @@
         <v>128</v>
       </c>
       <c r="D167" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="E167" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4584,7 +4626,7 @@
         <v>85</v>
       </c>
       <c r="D177" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="E177" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4602,7 +4644,7 @@
         <v>61</v>
       </c>
       <c r="D178" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="E178" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4620,7 +4662,7 @@
         <v>61</v>
       </c>
       <c r="D179" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="E179" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4638,7 +4680,7 @@
         <v>61</v>
       </c>
       <c r="D180" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="E180" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4656,7 +4698,7 @@
         <v>61</v>
       </c>
       <c r="D181" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="E181" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4674,7 +4716,7 @@
         <v>18</v>
       </c>
       <c r="D182" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="E182" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4692,7 +4734,7 @@
         <v>129</v>
       </c>
       <c r="D183" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="E183" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4710,7 +4752,7 @@
         <v>18</v>
       </c>
       <c r="D184" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E184" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4728,7 +4770,7 @@
         <v>18</v>
       </c>
       <c r="D185" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E185" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4746,7 +4788,7 @@
         <v>129</v>
       </c>
       <c r="D186" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E186" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4764,7 +4806,7 @@
         <v>61</v>
       </c>
       <c r="D187" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E187" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4782,7 +4824,7 @@
         <v>18</v>
       </c>
       <c r="D188" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E188" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4800,7 +4842,7 @@
         <v>18</v>
       </c>
       <c r="D189" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E189" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4818,7 +4860,7 @@
         <v>129</v>
       </c>
       <c r="D190" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E190" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4836,7 +4878,7 @@
         <v>85</v>
       </c>
       <c r="D191" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="E191" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4854,7 +4896,7 @@
         <v>126</v>
       </c>
       <c r="D192" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="E192" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4872,7 +4914,7 @@
         <v>130</v>
       </c>
       <c r="D193" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="E193" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4890,7 +4932,7 @@
         <v>126</v>
       </c>
       <c r="D194" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="E194" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4908,7 +4950,7 @@
         <v>126</v>
       </c>
       <c r="D195" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="E195" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4926,7 +4968,7 @@
         <v>126</v>
       </c>
       <c r="D196" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="E196" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4944,7 +4986,7 @@
         <v>126</v>
       </c>
       <c r="D197" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="E197" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4962,7 +5004,7 @@
         <v>126</v>
       </c>
       <c r="D198" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="E198" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4980,7 +5022,7 @@
         <v>126</v>
       </c>
       <c r="D199" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="E199" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -4998,7 +5040,7 @@
         <v>18</v>
       </c>
       <c r="D200" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="E200" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5016,7 +5058,7 @@
         <v>18</v>
       </c>
       <c r="D201" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="E201" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5034,7 +5076,7 @@
         <v>18</v>
       </c>
       <c r="D202" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="E202" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5052,7 +5094,7 @@
         <v>18</v>
       </c>
       <c r="D203" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="E203" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5070,7 +5112,7 @@
         <v>61</v>
       </c>
       <c r="D204" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="E204" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5088,7 +5130,7 @@
         <v>129</v>
       </c>
       <c r="D205" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="E205" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5106,7 +5148,7 @@
         <v>129</v>
       </c>
       <c r="D206" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="E206" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5124,7 +5166,7 @@
         <v>129</v>
       </c>
       <c r="D207" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="E207" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5232,7 +5274,7 @@
         <v>61</v>
       </c>
       <c r="D213" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E213" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5250,7 +5292,7 @@
         <v>129</v>
       </c>
       <c r="D214" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E214" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5268,7 +5310,7 @@
         <v>18</v>
       </c>
       <c r="D215" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E215" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5286,7 +5328,7 @@
         <v>129</v>
       </c>
       <c r="D216" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E216" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5304,7 +5346,7 @@
         <v>129</v>
       </c>
       <c r="D217" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E217" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5322,7 +5364,7 @@
         <v>129</v>
       </c>
       <c r="D218" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E218" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5340,7 +5382,7 @@
         <v>129</v>
       </c>
       <c r="D219" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E219" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5358,7 +5400,7 @@
         <v>129</v>
       </c>
       <c r="D220" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E220" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5376,7 +5418,7 @@
         <v>129</v>
       </c>
       <c r="D221" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E221" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5394,7 +5436,7 @@
         <v>61</v>
       </c>
       <c r="D222" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="E222" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5412,7 +5454,7 @@
         <v>61</v>
       </c>
       <c r="D223" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="E223" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5430,7 +5472,7 @@
         <v>61</v>
       </c>
       <c r="D224" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="E224" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5448,7 +5490,7 @@
         <v>61</v>
       </c>
       <c r="D225" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="E225" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5466,7 +5508,7 @@
         <v>18</v>
       </c>
       <c r="D226" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="E226" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5484,7 +5526,7 @@
         <v>18</v>
       </c>
       <c r="D227" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="E227" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -5502,7 +5544,7 @@
         <v>129</v>
       </c>
       <c r="D228" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="E228" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6060,7 +6102,7 @@
         <v>61</v>
       </c>
       <c r="D259" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E259" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6078,7 +6120,7 @@
         <v>61</v>
       </c>
       <c r="D260" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E260" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6096,7 +6138,7 @@
         <v>61</v>
       </c>
       <c r="D261" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E261" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6114,7 +6156,7 @@
         <v>61</v>
       </c>
       <c r="D262" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E262" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6132,7 +6174,7 @@
         <v>61</v>
       </c>
       <c r="D263" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E263" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6150,7 +6192,7 @@
         <v>61</v>
       </c>
       <c r="D264" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E264" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6168,7 +6210,7 @@
         <v>129</v>
       </c>
       <c r="D265" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E265" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6186,7 +6228,7 @@
         <v>129</v>
       </c>
       <c r="D266" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E266" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6204,7 +6246,7 @@
         <v>129</v>
       </c>
       <c r="D267" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E267" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6222,7 +6264,7 @@
         <v>61</v>
       </c>
       <c r="D268" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E268" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6240,7 +6282,7 @@
         <v>61</v>
       </c>
       <c r="D269" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E269" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6258,7 +6300,7 @@
         <v>61</v>
       </c>
       <c r="D270" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E270" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6276,7 +6318,7 @@
         <v>61</v>
       </c>
       <c r="D271" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E271" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6294,7 +6336,7 @@
         <v>61</v>
       </c>
       <c r="D272" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E272" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6312,7 +6354,7 @@
         <v>18</v>
       </c>
       <c r="D273" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E273" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6330,7 +6372,7 @@
         <v>129</v>
       </c>
       <c r="D274" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E274" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6348,7 +6390,7 @@
         <v>129</v>
       </c>
       <c r="D275" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E275" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6366,7 +6408,7 @@
         <v>128</v>
       </c>
       <c r="D276" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E276" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6384,7 +6426,7 @@
         <v>128</v>
       </c>
       <c r="D277" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E277" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6402,7 +6444,7 @@
         <v>61</v>
       </c>
       <c r="D278" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E278" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6420,7 +6462,7 @@
         <v>129</v>
       </c>
       <c r="D279" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E279" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6438,7 +6480,7 @@
         <v>129</v>
       </c>
       <c r="D280" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E280" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6456,7 +6498,7 @@
         <v>129</v>
       </c>
       <c r="D281" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E281" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6474,7 +6516,7 @@
         <v>129</v>
       </c>
       <c r="D282" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E282" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6492,7 +6534,7 @@
         <v>129</v>
       </c>
       <c r="D283" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E283" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6510,7 +6552,7 @@
         <v>129</v>
       </c>
       <c r="D284" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E284" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6528,7 +6570,7 @@
         <v>129</v>
       </c>
       <c r="D285" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E285" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6546,7 +6588,7 @@
         <v>129</v>
       </c>
       <c r="D286" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E286" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6564,7 +6606,7 @@
         <v>128</v>
       </c>
       <c r="D287" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E287" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6582,7 +6624,7 @@
         <v>85</v>
       </c>
       <c r="D288" t="s">
-        <v>9</v>
+        <v>144</v>
       </c>
       <c r="E288" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6600,7 +6642,7 @@
         <v>85</v>
       </c>
       <c r="D289" t="s">
-        <v>9</v>
+        <v>144</v>
       </c>
       <c r="E289" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6618,7 +6660,7 @@
         <v>85</v>
       </c>
       <c r="D290" t="s">
-        <v>9</v>
+        <v>144</v>
       </c>
       <c r="E290" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6636,7 +6678,7 @@
         <v>126</v>
       </c>
       <c r="D291" t="s">
-        <v>9</v>
+        <v>144</v>
       </c>
       <c r="E291" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6654,7 +6696,7 @@
         <v>61</v>
       </c>
       <c r="D292" t="s">
-        <v>9</v>
+        <v>144</v>
       </c>
       <c r="E292" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6672,7 +6714,7 @@
         <v>61</v>
       </c>
       <c r="D293" t="s">
-        <v>9</v>
+        <v>144</v>
       </c>
       <c r="E293" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6690,7 +6732,7 @@
         <v>61</v>
       </c>
       <c r="D294" t="s">
-        <v>9</v>
+        <v>144</v>
       </c>
       <c r="E294" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6708,7 +6750,7 @@
         <v>61</v>
       </c>
       <c r="D295" t="s">
-        <v>9</v>
+        <v>144</v>
       </c>
       <c r="E295" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6726,7 +6768,7 @@
         <v>61</v>
       </c>
       <c r="D296" t="s">
-        <v>9</v>
+        <v>144</v>
       </c>
       <c r="E296" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6744,7 +6786,7 @@
         <v>61</v>
       </c>
       <c r="D297" t="s">
-        <v>9</v>
+        <v>144</v>
       </c>
       <c r="E297" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6762,7 +6804,7 @@
         <v>61</v>
       </c>
       <c r="D298" t="s">
-        <v>9</v>
+        <v>144</v>
       </c>
       <c r="E298" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6780,7 +6822,7 @@
         <v>129</v>
       </c>
       <c r="D299" t="s">
-        <v>9</v>
+        <v>144</v>
       </c>
       <c r="E299" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -6798,7 +6840,7 @@
         <v>128</v>
       </c>
       <c r="D300" t="s">
-        <v>9</v>
+        <v>144</v>
       </c>
       <c r="E300" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7302,7 +7344,7 @@
         <v>61</v>
       </c>
       <c r="D328" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="E328" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7320,7 +7362,7 @@
         <v>61</v>
       </c>
       <c r="D329" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="E329" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7338,7 +7380,7 @@
         <v>61</v>
       </c>
       <c r="D330" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="E330" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7356,7 +7398,7 @@
         <v>61</v>
       </c>
       <c r="D331" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="E331" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7374,7 +7416,7 @@
         <v>61</v>
       </c>
       <c r="D332" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="E332" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7392,7 +7434,7 @@
         <v>61</v>
       </c>
       <c r="D333" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="E333" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7410,7 +7452,7 @@
         <v>61</v>
       </c>
       <c r="D334" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="E334" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7428,7 +7470,7 @@
         <v>61</v>
       </c>
       <c r="D335" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="E335" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7446,7 +7488,7 @@
         <v>61</v>
       </c>
       <c r="D336" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="E336" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7464,7 +7506,7 @@
         <v>18</v>
       </c>
       <c r="D337" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="E337" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7482,7 +7524,7 @@
         <v>18</v>
       </c>
       <c r="D338" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="E338" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7500,7 +7542,7 @@
         <v>18</v>
       </c>
       <c r="D339" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="E339" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7518,7 +7560,7 @@
         <v>61</v>
       </c>
       <c r="D340" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="E340" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7536,7 +7578,7 @@
         <v>18</v>
       </c>
       <c r="D341" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="E341" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7554,7 +7596,7 @@
         <v>129</v>
       </c>
       <c r="D342" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="E342" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7572,7 +7614,7 @@
         <v>61</v>
       </c>
       <c r="D343" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="E343" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7590,7 +7632,7 @@
         <v>61</v>
       </c>
       <c r="D344" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="E344" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7608,7 +7650,7 @@
         <v>61</v>
       </c>
       <c r="D345" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="E345" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7968,7 +8010,7 @@
         <v>61</v>
       </c>
       <c r="D365" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="E365" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -7986,7 +8028,7 @@
         <v>85</v>
       </c>
       <c r="D366" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="E366" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -8004,7 +8046,7 @@
         <v>61</v>
       </c>
       <c r="D367" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="E367" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -8022,7 +8064,7 @@
         <v>18</v>
       </c>
       <c r="D368" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="E368" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -8040,7 +8082,7 @@
         <v>61</v>
       </c>
       <c r="D369" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="E369" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -8058,7 +8100,7 @@
         <v>18</v>
       </c>
       <c r="D370" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="E370" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -8076,7 +8118,7 @@
         <v>129</v>
       </c>
       <c r="D371" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="E371" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -8094,7 +8136,7 @@
         <v>129</v>
       </c>
       <c r="D372" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="E372" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -8112,7 +8154,7 @@
         <v>129</v>
       </c>
       <c r="D373" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="E373" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -8130,7 +8172,7 @@
         <v>129</v>
       </c>
       <c r="D374" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="E374" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -8145,10 +8187,10 @@
         <v>42570</v>
       </c>
       <c r="C375" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D375" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="E375" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -8166,7 +8208,7 @@
         <v>129</v>
       </c>
       <c r="D376" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="E376" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -8184,7 +8226,7 @@
         <v>128</v>
       </c>
       <c r="D377" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="E377" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -8201,9 +8243,6 @@
       <c r="C378" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D378" t="s">
-        <v>133</v>
-      </c>
       <c r="E378" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
         <v>2016-08-13</v>
@@ -8219,9 +8258,6 @@
       <c r="C379" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D379" t="s">
-        <v>133</v>
-      </c>
       <c r="E379" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
         <v>2016-08-14</v>
@@ -8237,9 +8273,6 @@
       <c r="C380" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D380" t="s">
-        <v>133</v>
-      </c>
       <c r="E380" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
         <v>2016-08-15</v>
@@ -8255,9 +8288,6 @@
       <c r="C381" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D381" t="s">
-        <v>133</v>
-      </c>
       <c r="E381" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
         <v>2016-08-16</v>
@@ -8273,9 +8303,6 @@
       <c r="C382" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D382" t="s">
-        <v>133</v>
-      </c>
       <c r="E382" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
         <v>2016-08-17</v>
@@ -8418,7 +8445,7 @@
         <v>61</v>
       </c>
       <c r="D390" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E390" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -8436,7 +8463,7 @@
         <v>61</v>
       </c>
       <c r="D391" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E391" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -8454,7 +8481,7 @@
         <v>61</v>
       </c>
       <c r="D392" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E392" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -8472,7 +8499,7 @@
         <v>129</v>
       </c>
       <c r="D393" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E393" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -8490,7 +8517,7 @@
         <v>129</v>
       </c>
       <c r="D394" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E394" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9102,7 +9129,7 @@
         <v>18</v>
       </c>
       <c r="D428" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="E428" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9120,7 +9147,7 @@
         <v>18</v>
       </c>
       <c r="D429" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="E429" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9138,7 +9165,7 @@
         <v>18</v>
       </c>
       <c r="D430" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="E430" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9156,7 +9183,7 @@
         <v>18</v>
       </c>
       <c r="D431" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="E431" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9174,7 +9201,7 @@
         <v>18</v>
       </c>
       <c r="D432" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="E432" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9192,7 +9219,7 @@
         <v>18</v>
       </c>
       <c r="D433" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="E433" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9210,7 +9237,7 @@
         <v>129</v>
       </c>
       <c r="D434" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="E434" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9228,7 +9255,7 @@
         <v>129</v>
       </c>
       <c r="D435" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="E435" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9246,7 +9273,7 @@
         <v>129</v>
       </c>
       <c r="D436" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="E436" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9264,7 +9291,7 @@
         <v>129</v>
       </c>
       <c r="D437" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="E437" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9282,7 +9309,7 @@
         <v>129</v>
       </c>
       <c r="D438" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="E438" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9300,7 +9327,7 @@
         <v>129</v>
       </c>
       <c r="D439" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="E439" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9318,7 +9345,7 @@
         <v>129</v>
       </c>
       <c r="D440" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="E440" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9336,7 +9363,7 @@
         <v>129</v>
       </c>
       <c r="D441" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="E441" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9354,7 +9381,7 @@
         <v>18</v>
       </c>
       <c r="D442" t="s">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="E442" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9372,7 +9399,7 @@
         <v>18</v>
       </c>
       <c r="D443" t="s">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="E443" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9390,7 +9417,7 @@
         <v>18</v>
       </c>
       <c r="D444" t="s">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="E444" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9408,7 +9435,7 @@
         <v>18</v>
       </c>
       <c r="D445" t="s">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="E445" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9426,7 +9453,7 @@
         <v>129</v>
       </c>
       <c r="D446" t="s">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="E446" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
@@ -9444,7 +9471,7 @@
         <v>129</v>
       </c>
       <c r="D447" t="s">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="E447" t="str">
         <f>TEXT(Table1_14[[#This Row],[date]]+1,"yyyy-mm-dd")</f>
